--- a/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 19,76</t>
+          <t>-7,67; 19,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 5,68</t>
+          <t>-17,08; 5,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,24; 61,43</t>
+          <t>34,47; 61,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 12,44</t>
+          <t>-12,29; 13,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 4,39</t>
+          <t>-18,27; 4,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,37; 59,58</t>
+          <t>34,08; 60,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 12,49</t>
+          <t>-5,24; 13,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 1,63</t>
+          <t>-14,97; 2,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,2; 57,0</t>
+          <t>38,66; 57,33</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 147,06</t>
+          <t>-32,59; 143,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 49,6</t>
+          <t>-62,39; 45,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,91; 480,06</t>
+          <t>125,58; 477,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 85,03</t>
+          <t>-43,41; 93,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 32,14</t>
+          <t>-64,82; 29,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>105,18; 399,78</t>
+          <t>112,32; 398,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 73,4</t>
+          <t>-19,88; 81,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 9,64</t>
+          <t>-58,46; 14,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>137,55; 355,07</t>
+          <t>141,23; 355,69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 5,83</t>
+          <t>-12,5; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 12,26</t>
+          <t>-7,54; 11,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 48,83</t>
+          <t>-7,23; 47,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 12,07</t>
+          <t>-3,82; 11,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,37</t>
+          <t>-4,68; 10,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 9,2</t>
+          <t>-7,53; 7,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,58</t>
+          <t>-5,29; 7,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 8,48</t>
+          <t>-3,58; 7,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 35,1</t>
+          <t>-3,31; 32,3</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 35,4</t>
+          <t>-46,61; 33,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 67,36</t>
+          <t>-26,99; 70,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 293,07</t>
+          <t>-31,4; 298,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 128,33</t>
+          <t>-23,97; 125,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 114,31</t>
+          <t>-28,69; 123,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 100,14</t>
+          <t>-44,01; 69,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 45,18</t>
+          <t>-26,53; 47,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 60,26</t>
+          <t>-16,41; 51,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 225,49</t>
+          <t>-19,05; 235,51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,89; -2,44</t>
+          <t>-27,67; -2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 6,67</t>
+          <t>-20,71; 6,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,06; -7,84</t>
+          <t>-31,28; -7,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 5,35</t>
+          <t>-16,03; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 8,24</t>
+          <t>-12,21; 8,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -1,12</t>
+          <t>-19,12; -0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -1,53</t>
+          <t>-17,58; -1,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 4,42</t>
+          <t>-13,5; 3,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -6,63</t>
+          <t>-22,0; -7,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,48; -8,29</t>
+          <t>-69,88; -6,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 27,46</t>
+          <t>-52,46; 30,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,3; -28,03</t>
+          <t>-82,25; -26,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,52; 39,04</t>
+          <t>-60,71; 35,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 54,43</t>
+          <t>-48,98; 61,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,79; -3,5</t>
+          <t>-74,03; 0,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,6; -5,84</t>
+          <t>-59,2; -7,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 22,37</t>
+          <t>-44,22; 14,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,19; -30,93</t>
+          <t>-72,84; -31,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 4,01</t>
+          <t>-15,49; 3,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 20,81</t>
+          <t>-2,25; 20,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 5,61</t>
+          <t>-15,22; 5,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -3,28</t>
+          <t>-19,25; -3,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 9,66</t>
+          <t>-9,85; 9,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 40,12</t>
+          <t>-10,48; 36,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -1,7</t>
+          <t>-15,13; -2,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 11,67</t>
+          <t>-3,17; 11,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 18,73</t>
+          <t>-8,42; 20,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 29,25</t>
+          <t>-63,4; 31,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 141,84</t>
+          <t>-11,96; 159,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 42,45</t>
+          <t>-61,99; 40,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,37; -23,26</t>
+          <t>-84,3; -23,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 70,45</t>
+          <t>-43,16; 79,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 353,28</t>
+          <t>-56,47; 282,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,72; -11,06</t>
+          <t>-68,91; -13,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 85,03</t>
+          <t>-15,85; 79,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 123,42</t>
+          <t>-43,52; 160,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-43,81; -12,12</t>
+          <t>-41,54; -12,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -20,63</t>
+          <t>-50,3; -20,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-58,9; -32,68</t>
+          <t>-58,27; -33,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -10,51</t>
+          <t>-40,55; -10,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -12,91</t>
+          <t>-43,01; -13,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-49,82; -26,2</t>
+          <t>-51,33; -27,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-37,27; -16,74</t>
+          <t>-37,7; -16,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -21,18</t>
+          <t>-41,29; -20,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -33,76</t>
+          <t>-50,27; -33,26</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,66; -31,23</t>
+          <t>-80,17; -32,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,61; -49,25</t>
+          <t>-91,53; -52,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,39 +1662,39 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-82,54; -31,76</t>
+          <t>-83,51; -32,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,71; -35,46</t>
+          <t>-86,26; -37,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -78,24</t>
+          <t>-100,0; -79,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -45,42</t>
+          <t>-76,86; -43,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,49; -54,98</t>
+          <t>-84,83; -52,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -90,64</t>
+          <t>-100,0; -89,46</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 5,58</t>
+          <t>-18,91; 5,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -0,58</t>
+          <t>-23,71; -1,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 6,3</t>
+          <t>-17,55; 5,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 7,35</t>
+          <t>-16,87; 6,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -3,31</t>
+          <t>-24,14; -1,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 5,84</t>
+          <t>-16,59; 6,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 2,15</t>
+          <t>-14,97; 2,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -5,52</t>
+          <t>-21,2; -5,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 2,64</t>
+          <t>-13,33; 2,88</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 39,02</t>
+          <t>-64,4; 35,81</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,11; -1,14</t>
+          <t>-81,39; -6,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 40,32</t>
+          <t>-58,6; 30,82</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 45,51</t>
+          <t>-60,27; 38,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,22; -11,47</t>
+          <t>-82,32; -5,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,86; 37,24</t>
+          <t>-56,86; 41,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 12,59</t>
+          <t>-53,76; 12,0</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-76,17; -27,54</t>
+          <t>-77,0; -26,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 14,0</t>
+          <t>-47,54; 17,87</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 5,08</t>
+          <t>-12,16; 5,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 5,37</t>
+          <t>-11,89; 5,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 0,97</t>
+          <t>-16,93; 0,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,28; -4,17</t>
+          <t>-19,92; -3,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -3,73</t>
+          <t>-21,1; -4,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-28,94; -12,96</t>
+          <t>-28,66; -13,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -1,84</t>
+          <t>-14,16; -1,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -2,18</t>
+          <t>-13,86; -2,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -9,23</t>
+          <t>-21,07; -9,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 24,32</t>
+          <t>-40,5; 24,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 28,02</t>
+          <t>-40,47; 25,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 5,4</t>
+          <t>-57,91; 3,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,89; -13,89</t>
+          <t>-56,45; -10,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,09; -13,81</t>
+          <t>-59,36; -14,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,66; -48,08</t>
+          <t>-81,01; -48,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -6,53</t>
+          <t>-44,74; -6,14</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,8; -8,11</t>
+          <t>-44,28; -9,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,59; -35,15</t>
+          <t>-66,95; -36,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 6,64</t>
+          <t>-8,87; 6,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 8,3</t>
+          <t>-6,28; 8,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -6,96</t>
+          <t>-21,39; -7,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -2,25</t>
+          <t>-16,83; -2,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 1,59</t>
+          <t>-12,35; 2,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,58; -10,25</t>
+          <t>-22,49; -9,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 0,38</t>
+          <t>-10,28; 0,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 3,93</t>
+          <t>-7,37; 2,98</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -10,23</t>
+          <t>-20,05; -10,52</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 30,73</t>
+          <t>-30,03; 33,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 40,43</t>
+          <t>-21,74; 42,63</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,58; -32,03</t>
+          <t>-72,78; -32,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-58,55; -10,47</t>
+          <t>-60,4; -12,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 8,29</t>
+          <t>-44,36; 12,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-83,13; -48,76</t>
+          <t>-82,45; -47,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 1,92</t>
+          <t>-39,05; 0,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 18,7</t>
+          <t>-27,36; 14,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,35; -47,81</t>
+          <t>-74,66; -48,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -1,05</t>
+          <t>-9,12; -1,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,31</t>
+          <t>-6,98; 0,18</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 9,66</t>
+          <t>-7,25; 9,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -4,36</t>
+          <t>-10,8; -4,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -3,37</t>
+          <t>-9,94; -3,15</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,8</t>
+          <t>-9,1; -1,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -3,79</t>
+          <t>-8,7; -3,77</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -2,43</t>
+          <t>-7,51; -2,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 1,32</t>
+          <t>-7,09; 1,64</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -4,38</t>
+          <t>-33,24; -6,87</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 1,27</t>
+          <t>-25,87; 0,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 38,39</t>
+          <t>-27,24; 40,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -19,22</t>
+          <t>-43,37; -19,05</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -15,81</t>
+          <t>-39,48; -14,66</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -2,86</t>
+          <t>-36,66; -3,81</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-34,85; -16,41</t>
+          <t>-33,7; -16,19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -10,78</t>
+          <t>-29,17; -10,86</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 5,63</t>
+          <t>-28,18; 7,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 19,34</t>
+          <t>-5,08; 21,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 5,85</t>
+          <t>-16,26; 6,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,47; 61,35</t>
+          <t>35,57; 62,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 13,95</t>
+          <t>-12,42; 12,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 4,54</t>
+          <t>-18,53; 3,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,08; 60,62</t>
+          <t>33,7; 58,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,34</t>
+          <t>-6,26; 12,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 2,29</t>
+          <t>-14,45; 2,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,66; 57,33</t>
+          <t>36,93; 57,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 143,22</t>
+          <t>-22,66; 153,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 45,65</t>
+          <t>-62,65; 47,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125,58; 477,11</t>
+          <t>126,6; 470,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 93,87</t>
+          <t>-45,95; 78,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 29,85</t>
+          <t>-66,17; 24,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>112,32; 398,16</t>
+          <t>109,08; 380,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 81,88</t>
+          <t>-24,23; 76,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 14,19</t>
+          <t>-56,09; 13,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141,23; 355,69</t>
+          <t>135,9; 349,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 5,54</t>
+          <t>-12,25; 6,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 11,65</t>
+          <t>-6,29; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 47,02</t>
+          <t>-7,61; 47,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 11,55</t>
+          <t>-4,21; 11,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,65</t>
+          <t>-5,29; 10,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 7,08</t>
+          <t>-7,12; 7,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,13</t>
+          <t>-5,74; 6,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 7,66</t>
+          <t>-4,26; 8,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 32,3</t>
+          <t>-4,34; 31,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 33,86</t>
+          <t>-44,93; 35,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 70,29</t>
+          <t>-24,12; 69,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 298,69</t>
+          <t>-33,76; 265,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 125,87</t>
+          <t>-25,43; 128,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 123,04</t>
+          <t>-32,39; 116,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 69,31</t>
+          <t>-44,96; 77,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 47,4</t>
+          <t>-26,85; 42,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 51,43</t>
+          <t>-20,28; 58,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 235,51</t>
+          <t>-23,39; 205,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -2,13</t>
+          <t>-26,34; -2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 6,68</t>
+          <t>-19,42; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -7,18</t>
+          <t>-30,51; -7,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 5,12</t>
+          <t>-15,15; 4,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 8,86</t>
+          <t>-11,91; 9,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -0,01</t>
+          <t>-18,27; 1,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -1,55</t>
+          <t>-17,8; -2,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 3,35</t>
+          <t>-12,93; 3,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -7,19</t>
+          <t>-22,08; -7,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,88; -6,65</t>
+          <t>-69,5; -7,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 30,6</t>
+          <t>-52,02; 29,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,25; -26,82</t>
+          <t>-81,56; -31,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 35,58</t>
+          <t>-59,09; 34,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,98; 61,7</t>
+          <t>-47,46; 60,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,03; 0,24</t>
+          <t>-72,23; 9,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,2; -7,05</t>
+          <t>-59,38; -10,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 14,75</t>
+          <t>-43,62; 16,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -31,25</t>
+          <t>-73,76; -34,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 3,86</t>
+          <t>-15,74; 3,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 20,72</t>
+          <t>-2,42; 21,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 5,36</t>
+          <t>-14,29; 6,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,25; -3,92</t>
+          <t>-18,76; -3,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 9,54</t>
+          <t>-9,56; 10,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 36,94</t>
+          <t>-10,45; 36,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -2,31</t>
+          <t>-15,41; -2,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 11,42</t>
+          <t>-3,09; 11,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 20,42</t>
+          <t>-8,54; 20,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 31,55</t>
+          <t>-63,13; 29,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 159,55</t>
+          <t>-11,54; 148,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 40,14</t>
+          <t>-62,78; 45,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,3; -23,96</t>
+          <t>-85,36; -22,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 79,01</t>
+          <t>-44,29; 84,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 282,35</t>
+          <t>-54,99; 347,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,91; -13,92</t>
+          <t>-69,77; -15,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 79,05</t>
+          <t>-14,56; 75,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 160,08</t>
+          <t>-44,11; 130,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -12,72</t>
+          <t>-42,9; -12,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-50,3; -20,49</t>
+          <t>-48,26; -18,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-58,27; -33,91</t>
+          <t>-57,29; -33,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -10,77</t>
+          <t>-39,95; -9,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,01; -13,98</t>
+          <t>-42,14; -13,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -27,17</t>
+          <t>-51,45; -26,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-37,7; -16,4</t>
+          <t>-36,33; -14,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -20,62</t>
+          <t>-40,59; -20,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -33,26</t>
+          <t>-50,73; -34,06</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,17; -32,75</t>
+          <t>-81,76; -33,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-91,53; -52,17</t>
+          <t>-90,74; -48,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-83,51; -32,93</t>
+          <t>-83,19; -29,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,26; -37,15</t>
+          <t>-86,26; -39,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -79,99</t>
+          <t>-100,0; -79,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-76,86; -43,25</t>
+          <t>-77,71; -42,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,83; -52,15</t>
+          <t>-84,76; -54,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -89,46</t>
+          <t>-100,0; -88,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 5,85</t>
+          <t>-18,28; 5,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -1,93</t>
+          <t>-24,25; -1,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 5,35</t>
+          <t>-18,01; 6,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 6,63</t>
+          <t>-15,71; 8,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,14; -1,99</t>
+          <t>-24,86; -2,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 6,84</t>
+          <t>-14,89; 7,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 2,25</t>
+          <t>-13,96; 2,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -5,66</t>
+          <t>-20,73; -5,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 2,88</t>
+          <t>-12,8; 3,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 35,81</t>
+          <t>-63,33; 38,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-81,39; -6,84</t>
+          <t>-79,65; -4,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 30,82</t>
+          <t>-60,78; 40,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 38,45</t>
+          <t>-56,28; 52,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,32; -5,21</t>
+          <t>-82,15; -8,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 41,67</t>
+          <t>-52,73; 43,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 12,0</t>
+          <t>-51,01; 15,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -26,12</t>
+          <t>-76,16; -28,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 17,87</t>
+          <t>-46,63; 20,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 5,13</t>
+          <t>-12,02; 5,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 5,33</t>
+          <t>-11,75; 5,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 0,56</t>
+          <t>-16,98; 1,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -3,11</t>
+          <t>-20,19; -3,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -4,2</t>
+          <t>-20,61; -3,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-28,66; -13,7</t>
+          <t>-28,76; -13,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -1,55</t>
+          <t>-13,8; -1,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -2,2</t>
+          <t>-13,86; -2,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -9,47</t>
+          <t>-21,73; -9,21</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 24,64</t>
+          <t>-39,26; 25,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 25,75</t>
+          <t>-39,9; 25,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 3,11</t>
+          <t>-58,14; 5,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,45; -10,22</t>
+          <t>-56,47; -9,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,36; -14,97</t>
+          <t>-58,22; -13,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,01; -48,85</t>
+          <t>-80,18; -48,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,74; -6,14</t>
+          <t>-44,3; -6,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,28; -9,29</t>
+          <t>-43,5; -6,82</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,95; -36,84</t>
+          <t>-67,8; -35,26</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 6,96</t>
+          <t>-8,52; 6,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 8,45</t>
+          <t>-6,56; 8,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-21,39; -7,21</t>
+          <t>-20,57; -7,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -2,79</t>
+          <t>-16,6; -3,45</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 2,42</t>
+          <t>-12,61; 1,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -9,73</t>
+          <t>-22,63; -9,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,21</t>
+          <t>-9,78; -0,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,98</t>
+          <t>-7,11; 3,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -10,52</t>
+          <t>-19,63; -10,58</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 33,95</t>
+          <t>-30,15; 31,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 42,63</t>
+          <t>-22,68; 41,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,78; -32,03</t>
+          <t>-73,71; -33,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-60,4; -12,49</t>
+          <t>-61,58; -16,65</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 12,46</t>
+          <t>-45,31; 9,21</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-82,45; -47,0</t>
+          <t>-81,28; -47,28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 0,97</t>
+          <t>-37,01; 0,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 14,68</t>
+          <t>-26,73; 15,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-74,66; -48,79</t>
+          <t>-73,59; -48,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,51</t>
+          <t>-9,05; -1,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,18</t>
+          <t>-7,13; 0,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 9,15</t>
+          <t>-7,26; 9,1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -4,13</t>
+          <t>-10,97; -3,99</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,15</t>
+          <t>-9,93; -3,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,0</t>
+          <t>-9,11; -1,07</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -3,77</t>
+          <t>-8,75; -3,63</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -2,51</t>
+          <t>-7,37; -2,57</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,64</t>
+          <t>-7,29; 1,3</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -6,87</t>
+          <t>-32,4; -7,15</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 0,61</t>
+          <t>-26,49; 1,72</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 40,97</t>
+          <t>-27,22; 36,41</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,37; -19,05</t>
+          <t>-43,18; -18,03</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -14,66</t>
+          <t>-39,49; -15,01</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -3,81</t>
+          <t>-36,26; -3,39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -16,19</t>
+          <t>-34,43; -16,05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-29,17; -10,86</t>
+          <t>-29,05; -11,03</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 7,27</t>
+          <t>-28,68; 6,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,0</t>
+          <t>41,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47,84</t>
+          <t>43,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 21,52</t>
+          <t>-13,1; 12,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 6,23</t>
+          <t>-19,36; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,57; 62,59</t>
+          <t>30,9; 58,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 12,55</t>
+          <t>-6,08; 19,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 3,05</t>
+          <t>-16,69; 5,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,7; 58,52</t>
+          <t>28,93; 55,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 12,65</t>
+          <t>-6,27; 12,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 2,05</t>
+          <t>-13,97; 1,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,93; 57,11</t>
+          <t>34,0; 52,49</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-32,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>201,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-24,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>244,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-32,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>211,0%</t>
+          <t>209,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225,57%</t>
+          <t>205,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 153,35</t>
+          <t>-43,94; 85,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 47,24</t>
+          <t>-66,2; 32,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126,6; 470,81</t>
+          <t>96,69; 385,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 78,81</t>
+          <t>-22,1; 147,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 24,51</t>
+          <t>-63,17; 49,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>109,08; 380,33</t>
+          <t>105,53; 411,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 76,2</t>
+          <t>-25,98; 73,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 13,52</t>
+          <t>-56,59; 9,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135,9; 349,74</t>
+          <t>125,91; 327,84</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-1,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,13</t>
+          <t>-3,41; 12,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 12,06</t>
+          <t>-4,77; 10,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 47,13</t>
+          <t>-8,13; 8,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 11,93</t>
+          <t>-12,56; 5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 10,56</t>
+          <t>-6,5; 12,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 7,51</t>
+          <t>-11,13; 8,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 6,39</t>
+          <t>-4,67; 6,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 8,38</t>
+          <t>-3,37; 8,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 31,03</t>
+          <t>-6,88; 5,53</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-2,75%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-14,11%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>-8,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>-6,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 35,58</t>
+          <t>-22,07; 128,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 69,8</t>
+          <t>-28,11; 114,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 265,5</t>
+          <t>-48,54; 98,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 128,94</t>
+          <t>-46,91; 35,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 116,36</t>
+          <t>-24,54; 67,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 77,97</t>
+          <t>-43,52; 52,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 42,43</t>
+          <t>-22,95; 45,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 58,46</t>
+          <t>-16,63; 60,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 205,7</t>
+          <t>-34,71; 36,98</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-10,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-14,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-6,9</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-19,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,7</t>
+          <t>-20,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,4</t>
+          <t>-15,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -2,41</t>
+          <t>-15,47; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 6,79</t>
+          <t>-12,45; 8,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,51; -7,73</t>
+          <t>-20,23; -2,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 4,93</t>
+          <t>-26,89; -2,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 9,11</t>
+          <t>-19,93; 6,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 1,19</t>
+          <t>-31,78; -9,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -2,42</t>
+          <t>-17,0; -1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,64</t>
+          <t>-11,86; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,08; -7,5</t>
+          <t>-22,4; -7,7</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-24,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,66%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-51,44%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-46,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-22,3%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-62,51%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-24,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-9,66%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,3%</t>
+          <t>-64,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-56,29%</t>
+          <t>-59,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,5; -7,61</t>
+          <t>-60,52; 39,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 29,4</t>
+          <t>-50,78; 54,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,56; -31,61</t>
+          <t>-75,74; -10,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 34,71</t>
+          <t>-70,48; -8,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 60,55</t>
+          <t>-52,7; 27,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 9,57</t>
+          <t>-82,8; -32,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,38; -10,59</t>
+          <t>-57,6; -5,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 16,79</t>
+          <t>-40,34; 22,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,76; -34,11</t>
+          <t>-74,24; -35,25</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-11,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,36</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-11,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>-0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 3,82</t>
+          <t>-19,23; -3,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 21,12</t>
+          <t>-10,68; 9,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 6,11</t>
+          <t>-10,29; 35,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -3,1</t>
+          <t>-16,55; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 10,13</t>
+          <t>-2,71; 20,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 36,7</t>
+          <t>-16,16; 5,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -2,65</t>
+          <t>-14,22; -1,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,19</t>
+          <t>-3,59; 11,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 20,96</t>
+          <t>-9,43; 14,31</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-64,1%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0,96%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-28,21%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>46,45%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-25,06%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-64,1%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-0,96%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>-26,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>-4,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 29,78</t>
+          <t>-85,37; -23,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 148,63</t>
+          <t>-48,26; 70,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 45,62</t>
+          <t>-57,22; 287,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,36; -22,6</t>
+          <t>-64,74; 29,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 84,49</t>
+          <t>-15,08; 141,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 347,64</t>
+          <t>-64,69; 41,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,77; -15,29</t>
+          <t>-65,72; -11,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 75,95</t>
+          <t>-17,01; 85,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 130,23</t>
+          <t>-45,83; 106,96</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-25,66</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-27,83</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-38,24</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-28,77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-34,96</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-45,88</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-25,66</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-27,83</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-38,59</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>-27,16</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-42,06</t>
+          <t>-41,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -12,31</t>
+          <t>-39,55; -10,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-48,26; -18,39</t>
+          <t>-41,54; -12,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-57,29; -33,35</t>
+          <t>-49,66; -25,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-39,95; -9,79</t>
+          <t>-43,81; -12,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -13,46</t>
+          <t>-48,87; -20,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-51,45; -26,66</t>
+          <t>-58,9; -32,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-36,33; -14,78</t>
+          <t>-37,27; -16,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -20,26</t>
+          <t>-41,98; -21,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,73; -34,06</t>
+          <t>-50,85; -33,51</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-63,47%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-68,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-94,59%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-62,69%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-76,2%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-63,47%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-68,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-95,44%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-63,06%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-97,68%</t>
+          <t>-97,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -33,17</t>
+          <t>-82,54; -31,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,74; -48,41</t>
+          <t>-86,71; -35,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; -77,12</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-80,66; -31,23</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-90,61; -49,25</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-83,19; -29,53</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-86,26; -39,64</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -79,43</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-77,71; -42,65</t>
+          <t>-78,21; -45,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,76; -54,7</t>
+          <t>-84,49; -54,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -88,31</t>
+          <t>-100,0; -90,23</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-13,36</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-6,24</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-6,72</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-12,53</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-5,95</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-13,36</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-8,14</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 5,45</t>
+          <t>-17,03; 7,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -1,68</t>
+          <t>-24,83; -3,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 6,35</t>
+          <t>-17,73; 3,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 8,79</t>
+          <t>-18,28; 5,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,86; -2,62</t>
+          <t>-24,42; -0,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 7,45</t>
+          <t>-20,29; 3,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 2,91</t>
+          <t>-14,75; 2,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,73; -5,58</t>
+          <t>-20,76; -5,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 3,41</t>
+          <t>-15,66; 0,66</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-20,61%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-57,36%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-26,79%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-29,3%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-54,66%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-25,93%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-20,61%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-57,36%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-18,76%</t>
+          <t>-35,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-21,93%</t>
+          <t>-30,97%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 38,34</t>
+          <t>-61,66; 45,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,65; -4,39</t>
+          <t>-81,22; -11,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 40,33</t>
+          <t>-59,07; 27,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 52,46</t>
+          <t>-64,62; 39,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,15; -8,82</t>
+          <t>-82,11; -1,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 43,92</t>
+          <t>-68,14; 22,37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 15,5</t>
+          <t>-51,92; 12,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-76,16; -28,21</t>
+          <t>-76,17; -27,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 20,69</t>
+          <t>-57,15; 3,96</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-11,72</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-12,3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-20,22</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-3,42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-3,51</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-8,58</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-11,72</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-12,3</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-21,14</t>
+          <t>-9,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-15,32</t>
+          <t>-14,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 5,56</t>
+          <t>-20,28; -4,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 5,11</t>
+          <t>-20,33; -3,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 1,05</t>
+          <t>-28,45; -12,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,19; -3,09</t>
+          <t>-11,89; 5,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -3,3</t>
+          <t>-11,94; 5,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-28,76; -13,35</t>
+          <t>-17,1; -0,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -1,56</t>
+          <t>-14,47; -1,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -2,15</t>
+          <t>-14,36; -2,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,73; -9,21</t>
+          <t>-20,48; -8,76</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-37,56%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-39,4%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-64,79%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-13,33%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-13,66%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-33,44%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-37,56%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-39,4%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-67,74%</t>
+          <t>-35,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-53,76%</t>
+          <t>-52,34%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 25,72</t>
+          <t>-56,89; -13,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 25,38</t>
+          <t>-58,09; -13,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 5,49</t>
+          <t>-78,94; -44,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,47; -9,73</t>
+          <t>-39,75; 24,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,22; -13,39</t>
+          <t>-40,19; 28,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,18; -48,93</t>
+          <t>-56,99; 1,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,3; -6,25</t>
+          <t>-44,47; -6,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,5; -6,82</t>
+          <t>-45,8; -8,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,8; -35,26</t>
+          <t>-64,77; -33,75</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-9,66</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-4,94</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-16,11</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,63</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1,05</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-13,93</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-9,66</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-4,94</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-16,1</t>
+          <t>-14,86</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-15,14</t>
+          <t>-15,55</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 6,78</t>
+          <t>-15,74; -2,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,8</t>
+          <t>-11,37; 1,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -7,06</t>
+          <t>-22,41; -10,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-16,6; -3,45</t>
+          <t>-8,28; 6,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 1,59</t>
+          <t>-6,53; 8,3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -9,83</t>
+          <t>-21,78; -7,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -0,0</t>
+          <t>-10,15; 0,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,27</t>
+          <t>-6,73; 3,93</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,63; -10,58</t>
+          <t>-19,99; -10,88</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-40,75%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-20,84%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-67,97%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-2,53%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-56,27%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-40,75%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-20,84%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-67,92%</t>
+          <t>-60,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-62,53%</t>
+          <t>-64,21%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 31,84</t>
+          <t>-58,55; -10,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 41,64</t>
+          <t>-42,58; 8,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,71; -33,0</t>
+          <t>-82,21; -48,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-61,58; -16,65</t>
+          <t>-28,25; 30,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 9,21</t>
+          <t>-22,74; 40,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-81,28; -47,28</t>
+          <t>-75,7; -35,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 0,15</t>
+          <t>-36,98; 1,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 15,63</t>
+          <t>-25,44; 18,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,59; -48,2</t>
+          <t>-74,44; -49,77</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-7,47</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-6,61</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-4,97</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-7,47</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-6,61</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,79</t>
+          <t>-11,07; -4,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,41</t>
+          <t>-9,96; -3,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 9,1</t>
+          <t>-10,3; -2,36</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -3,99</t>
+          <t>-8,28; -1,05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -3,12</t>
+          <t>-7,23; 0,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,07</t>
+          <t>-11,43; -3,81</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -3,63</t>
+          <t>-8,88; -3,79</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,57</t>
+          <t>-7,45; -2,43</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,3</t>
+          <t>-9,58; -4,18</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-31,9%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-28,24%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-29,33%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-19,64%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-13,19%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-7,45%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-31,9%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-28,24%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-23,61%</t>
+          <t>-29,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-29,42%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -7,15</t>
+          <t>-43,41; -19,22</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 1,72</t>
+          <t>-39,55; -15,81</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 36,41</t>
+          <t>-41,16; -10,07</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -18,03</t>
+          <t>-30,25; -4,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -15,01</t>
+          <t>-26,46; 1,27</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -3,39</t>
+          <t>-41,52; -15,81</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,05</t>
+          <t>-34,85; -16,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -11,03</t>
+          <t>-29,16; -10,78</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 6,01</t>
+          <t>-37,77; -17,73</t>
         </is>
       </c>
     </row>
